--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/挖坟_货币配置表_Dig_CurrencyConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/挖坟_货币配置表_Dig_CurrencyConfig.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Work\Cursor\Gravedigger2026\Gravedigger2026\Gravedigger2026\Assets\ConfigTables\Mode2\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\CursorGame_Git\Gravedigger2026\Gravedigger2026\Assets\ConfigTables\Mode2\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12280"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -200,14 +200,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -360,7 +353,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -370,6 +363,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="0.5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -669,154 +668,155 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1164,9 +1164,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="3"/>
   <cols>
-    <col min="2" max="2" width="17.875" customWidth="1"/>
+    <col min="2" max="2" width="29.2727272727273" customWidth="1"/>
+    <col min="3" max="3" width="23.1818181818182" customWidth="1"/>
+    <col min="4" max="4" width="17.4545454545455" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1226,128 +1228,128 @@
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" t="s">
+      <c r="A5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="2" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" t="s">
+      <c r="A6" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="2" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" t="s">
+      <c r="A7" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="2" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" t="s">
+      <c r="A8" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="2" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" t="s">
+      <c r="A9" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="2" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" t="s">
+      <c r="A10" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="2" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" t="s">
+      <c r="A11" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="2" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" t="s">
+      <c r="A12" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="2" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" t="s">
+      <c r="A13" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="2" t="s">
         <v>51</v>
       </c>
     </row>
